--- a/practice/module-3-finance-and-formulas.xlsx
+++ b/practice/module-3-finance-and-formulas.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Loan Model" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Broken Formulas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Tasks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Solutions" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +57,24 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +84,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000F6F3F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -98,6 +120,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2908,7 +2940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3109,6 +3141,235 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Self-check:</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Right-click any sheet tab → Unhide → Solutions to reveal the answer key. Try every task FIRST without peeking.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Solutions — Module 3 — Formulas &amp; Macros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>These are the expected formulas / results for each Tasks sheet item. Try the task FIRST in real Excel, then peek here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Expected solution / formula</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Where it lands</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16">
+        <f>XLOOKUP(D2, Products!$A$2:$A$7, Products!$B$2:$B$7, "Not found")</f>
+        <v/>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Sales!I2:I61</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Column I matches the Product Name from the Products lookup table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="16">
+        <f>IFS(H2&gt;=500,"A", H2&gt;=200,"B", TRUE,"C")</f>
+        <v/>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Sales!J2:J61</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Tier letter populates for every row; no #N/A or empty cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="16">
+        <f>FILTER(Sales!A2:H61, (Sales!E2:E61&gt;8)*(Sales!G2:G61&gt;0))</f>
+        <v/>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Any free cell with ~6 cols of room</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Result spills only orders matching both conditions; check by counting manually for a sample.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Data → What-If Analysis → Goal Seek. Set cell B6, To value 1200, By changing B2.</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Loan Model!B2</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Principal updates so PMT formula in B6 = 1200. Approx $189,851 at 6.5%/30y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>List rates in (e.g.) E3:E7. In F2 put =B6 (link to formula). Select E2:F7. Data → What-If → Data Table → Column input cell: B3.</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Loan Model!E2:F7 (or similar)</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Each rate row shows the corresponding PMT; values rise with rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Row 4: change index 6→2.  Row 5: =IFERROR(10/0, 0).  Row 6: re-reference correct cell, e.g. =A1*2.  Row 7: =SUM(Sales!E:E).  Row 8: ensure space below the formula to spill.</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Broken Formulas!C4:C8</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>All cells in column C return a number/text — none show #REF!, #DIV/0!, #NAME?, or #SPILL!.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Developer → Record Macro → Name: FormatHeader. While recording: Bold (Ctrl+B), Fill Green (Home → Fill Color), Font Color White. Stop. Save As .xlsm.</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Stored in Personal/this workbook macro module</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Running FormatHeader on any cell makes it bold, green-filled, white text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="16">
+        <f>SUMIFS(Sales!H:H, Sales!C:C,"CUST-001", Sales!D:D,"PRD-A*")</f>
+        <v/>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Any cell</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Cross-check: filter Sales for CUST-001 + Product Codes starting PRD-A and SUM column H.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>

--- a/practice/module-3-finance-and-formulas.xlsx
+++ b/practice/module-3-finance-and-formulas.xlsx
@@ -2940,7 +2940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3150,6 +3150,94 @@
       <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Right-click any sheet tab → Unhide → Solutions to reveal the answer key. Try every task FIRST without peeking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Monthly mortgage payment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PMT — find monthly payment for the Loan Model values</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Hint: =PMT(rate/12, term*12, -principal). Watch the sign convention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Months to pay off at $400/mo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NPER — solve for number of months given a fixed payment</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Hint: =NPER(rate/12, -monthly_payment, principal). Use 9% APR and $15,000 principal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Interest vs. principal in month 1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>IPMT and PPMT — split a payment</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Hint: =IPMT(rate/12, 1, term*12, principal) and =PPMT(...). Per=1 means month one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Annualised return on irregular cash flows</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>XIRR — irregular dates</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Hint: =XIRR(values, dates). Rows 2-4 of Loan Model column F.</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3370,6 +3458,90 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Monthly mortgage payment</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>PMT(rate/12, term_years*12, -principal)</f>
+        <v/>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Negative principal makes payment positive. With 6%/30y/$250k it's ≈ $1,498.88.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Months to pay off</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>NPER(0.09/12, -400, 15000)</f>
+        <v/>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Returns ≈ 47.06 months. Negative pmt because cash leaves your pocket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Interest vs. principal</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>IPMT(0.06/12, 1, 360, 250000)  and  =PPMT(0.06/12, 1, 360, 250000)</f>
+        <v/>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>IPMT is roughly -$1,250 (interest) and PPMT roughly -$248.88 (principal) on month 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Annualised return</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>XIRR(values_range, dates_range)</f>
+        <v/>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Result is a decimal — format as percentage. Verify by checking that NPV at that rate is ≈ 0.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
